--- a/dashboard/object_id.xlsx
+++ b/dashboard/object_id.xlsx
@@ -5,7 +5,8 @@
   <sheets>
     <sheet name="Page 1 UI Elements" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Page 2 UI Elements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Python Dicts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Page 10 UI Elements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Python Dicts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -997,7 +998,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>2</t>
@@ -1025,7 +1025,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>2</t>
@@ -1053,7 +1052,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>2</t>
@@ -1081,7 +1079,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>2</t>
@@ -1099,12 +1096,533 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A71"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>class_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>tireFLValue</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tireFRValue</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tireRLValue</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tireRRValue</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>maxCellValue</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>maxCellBar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>speedValue</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>psiFLValue</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>psiFRValue</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>psiRLValue</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>29</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>psiRRValue</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>socValue</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>socBar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>32</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>brakeBar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>33</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>throttleBar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>34</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>cardPitMode</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>badge</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A123"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t># id dictionary</t>
         </is>
       </c>
@@ -1252,336 +1770,700 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
+          <t xml:space="preserve">    # page_10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    19: "tireFLValue",</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t># uart_data dictionary</t>
+          <t xml:space="preserve">    20: "tireFRValue",</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>uart_data = {</t>
+          <t xml:space="preserve">    21: "tireRLValue",</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "frontbrakebar": 0,</t>
+          <t xml:space="preserve">    22: "tireRRValue",</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "rearbrakebar": 0,</t>
+          <t xml:space="preserve">    23: "maxCellValue",</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "speedbar": 0,</t>
+          <t xml:space="preserve">    24: "maxCellBar",</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "throttlebar": 0,</t>
+          <t xml:space="preserve">    25: "speedValue",</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "front_brake_text": 0,</t>
+          <t xml:space="preserve">    26: "psiFLValue",</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "rear_brake_text": 0,</t>
+          <t xml:space="preserve">    27: "psiFRValue",</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "speed_text": 0,</t>
+          <t xml:space="preserve">    28: "psiRLValue",</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "throttle_text": 0,</t>
+          <t xml:space="preserve">    29: "psiRRValue",</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">    # page_2</t>
+          <t xml:space="preserve">    30: "socValue",</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "valCurrent": 0,</t>
+          <t xml:space="preserve">    31: "socBar",</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "valVoltage": 0,</t>
+          <t xml:space="preserve">    32: "brakeBar",</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "valMinTemp": 0,</t>
+          <t xml:space="preserve">    33: "throttleBar",</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "valMaxTemp": 0,</t>
+          <t xml:space="preserve">    34: "cardPitMode",</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "valMinVolt": 0,</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "valMaxVolt": 0,</t>
-        </is>
-      </c>
-    </row>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "badgeCharging": 0,</t>
+          <t># uart_data dictionary</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "badgeBalancing": 0,</t>
+          <t>uart_data = {</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "dotCharging": 0,</t>
+          <t xml:space="preserve">    "frontbrakebar": 0,</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "dotBalancing": 0,</t>
+          <t xml:space="preserve">    "rearbrakebar": 0,</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
+          <t xml:space="preserve">    "speedbar": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "throttlebar": 0,</t>
+        </is>
+      </c>
+    </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t># pages dictionary</t>
+          <t xml:space="preserve">    "front_brake_text": 0,</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pages = {</t>
+          <t xml:space="preserve">    "rear_brake_text": 0,</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "page_1": {</t>
+          <t xml:space="preserve">    "speed_text": 0,</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "frontbrakebar": "bar",</t>
+          <t xml:space="preserve">    "throttle_text": 0,</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "rearbrakebar": "bar",</t>
+          <t xml:space="preserve">    # page_2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "speedbar": "bar",</t>
+          <t xml:space="preserve">    "valCurrent": 0,</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "throttlebar": "bar",</t>
+          <t xml:space="preserve">    "valVoltage": 0,</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "front_brake_text": "text",</t>
+          <t xml:space="preserve">    "valMinTemp": 0,</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "rear_brake_text": "text",</t>
+          <t xml:space="preserve">    "valMaxTemp": 0,</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "speed_text": "text",</t>
+          <t xml:space="preserve">    "valMinVolt": 0,</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "throttle_text": "text",</t>
+          <t xml:space="preserve">    "valMaxVolt": 0,</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">    "badgeCharging": 0,</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "page_2": {</t>
+          <t xml:space="preserve">    "badgeBalancing": 0,</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "valCurrent": "text",</t>
+          <t xml:space="preserve">    "dotCharging": 0,</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "valVoltage": "text",</t>
+          <t xml:space="preserve">    "dotBalancing": 0,</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "valMinTemp": "text",</t>
+          <t xml:space="preserve">    # page_10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "valMaxTemp": "text",</t>
+          <t xml:space="preserve">    "tireFLValue": 0,</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "valMinVolt": "text",</t>
+          <t xml:space="preserve">    "tireFRValue": 0,</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "valMaxVolt": "text",</t>
+          <t xml:space="preserve">    "tireRLValue": 0,</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "badgeCharging": "badge",</t>
+          <t xml:space="preserve">    "tireRRValue": 0,</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "badgeBalancing": "badge",</t>
+          <t xml:space="preserve">    "maxCellValue": 0,</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "dotCharging": "led",</t>
+          <t xml:space="preserve">    "maxCellBar": 0,</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "dotBalancing": "led",</t>
+          <t xml:space="preserve">    "speedValue": 0,</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">    "psiFLValue": 0,</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "psiFRValue": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "psiRLValue": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "psiRRValue": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "socValue": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "socBar": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "brakeBar": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "throttleBar": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "cardPitMode": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t># pages dictionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>pages = {</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "page_1": {</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "frontbrakebar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "rearbrakebar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "speedbar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "throttlebar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "front_brake_text": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "rear_brake_text": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "speed_text": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "throttle_text": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    },</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "page_2": {</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "valCurrent": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "valVoltage": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "valMinTemp": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "valMaxTemp": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "valMinVolt": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "valMaxVolt": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "badgeCharging": "badge",</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "badgeBalancing": "badge",</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "dotCharging": "led",</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "dotBalancing": "led",</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    },</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "page_10": {</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "tireFLValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "tireFRValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "tireRLValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "tireRRValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "maxCellValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "maxCellBar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "speedValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "psiFLValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "psiFRValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "psiRLValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "psiRRValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "socValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "socBar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "brakeBar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "throttleBar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "cardPitMode": "badge",</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    },</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>}</t>
         </is>

--- a/dashboard/object_id.xlsx
+++ b/dashboard/object_id.xlsx
@@ -5,8 +5,12 @@
   <sheets>
     <sheet name="Page 1 UI Elements" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Page 2 UI Elements" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Page 10 UI Elements" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Python Dicts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Page 3 UI Elements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Page 4 UI Elements" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Page 5 UI Elements" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Page 6 UI Elements" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Page 10 UI Elements" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Python Dicts" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1096,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,12 +1136,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>19</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>tireFLValue</t>
+          <t>packValue</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1152,22 +1158,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>20</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>tireFRValue</t>
+          <t>packMin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1182,22 +1190,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>21</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tireRLValue</t>
+          <t>packMax</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1212,27 +1222,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>22</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>tireRRValue</t>
+          <t>packBar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>progress_bar</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1242,22 +1254,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>23</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>maxCellValue</t>
+          <t>cellValue</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1272,27 +1286,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>24</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>maxCellBar</t>
+          <t>cellMin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1302,22 +1318,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>25</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>speedValue</t>
+          <t>cellMax</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1332,27 +1350,29 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>km/h</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>26</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>psiFLValue</t>
+          <t>cellBar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>progress_bar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1362,247 +1382,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSI</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>psiFRValue</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>PSI</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>28</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>psiRLValue</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>PSI</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>29</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>psiRRValue</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>PSI</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>30</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>socValue</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>31</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>socBar</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>32</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>brakeBar</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>33</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>throttleBar</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>34</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>cardPitMode</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>badge</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1617,124 +1402,2143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A123"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># id dictionary</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>class_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>page</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>id = {</t>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>running_perc</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1: "frontbrakebar",</t>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>gated_percent</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2: "rearbrakebar",</t>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>running_temp</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3: "speedbar",</t>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cur_max_temp</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>class_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>motorFLValue</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>motorFRValue</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>motorRLValue</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>motorRRValue</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4: "throttlebar",</t>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>igbtFLValue</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5: "front_brake_text",</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>igbtFRValue</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">    6: "rear_brake_text",</t>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>igbtRLValue</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">    7: "speed_text",</t>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>igbtRRValue</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">    8: "throttle_text",</t>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>coldPlateFLValue</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    # page_2</t>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>coldPlateFRValue</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    9:  "valCurrent",</t>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>coldPlateRLValue</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    10: "valVoltage",</t>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>coldPlateRRValue</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    11: "valMinTemp",</t>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>motorLoopStartValue</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    12: "valMaxTemp",</t>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>motorLoopEndValue</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    13: "valMinVolt",</t>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>inverterLoopStartValue</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>inverterLoopEndValue</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>class_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>can1_util_bar_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>progress_bar</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>can1_util_bar_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>progress_bar</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>can1_util_bar_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>progress_bar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>can1_util_bar_4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>progress_bar</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>barPercentStyle</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>barPercentStyle2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>barPercentStyle3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>barPercentStyle4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>tableRowValue</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>tableRowValue2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>tableRowValue3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>tableRowValue4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>l1_light</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>led</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>l2_light</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>led</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>l3_light</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>led</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>l4_light</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>led</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>class_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>default_value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>tireFLValue</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tireFRValue</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tireRLValue</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tireRRValue</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>maxCellValue</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>maxCellBar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>speedValue</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tempfl</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>tempfr</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>temprl</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>29</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>temprr</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>socValue</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>socBar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>32</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>brakeBar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>33</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>throttleBar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>34</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>cardPitMode</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>badge</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>35</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>torqueFL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Nm</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>36</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>torqueFR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Nm</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>37</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>torqueRL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Nm</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>38</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>torqueRR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Nm</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>39</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>torqueBarFL</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>progress_bar</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Nm</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>40</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>torqueBarFR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>progress_bar</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Nm</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>41</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>torqueBarRL</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>progress_bar</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Nm</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>42</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>torqueBarRR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>progress_bar</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Nm</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A195"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t># id dictionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>id = {</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    1: "frontbrakebar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    2: "rearbrakebar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    3: "speedbar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    4: "throttlebar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    5: "front_brake_text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    6: "rear_brake_text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    7: "speed_text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    8: "throttle_text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    # page_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    9:  "valCurrent",</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    10: "valVoltage",</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    11: "valMinTemp",</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    12: "valMaxTemp",</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    13: "valMinVolt",</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t xml:space="preserve">    14: "valMaxVolt",</t>
         </is>
       </c>
@@ -1770,700 +3574,1204 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">    # page_10</t>
+          <t xml:space="preserve">    # page_3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    19: "tireFLValue",</t>
+          <t xml:space="preserve">    43: "packValue",</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    20: "tireFRValue",</t>
+          <t xml:space="preserve">    44: "packMin",</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    21: "tireRLValue",</t>
+          <t xml:space="preserve">    45: "packMax",</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    22: "tireRRValue",</t>
+          <t xml:space="preserve">    46: "packBar",</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">    23: "maxCellValue",</t>
+          <t xml:space="preserve">    47: "cellValue",</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    24: "maxCellBar",</t>
+          <t xml:space="preserve">    48: "cellMin",</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">    25: "speedValue",</t>
+          <t xml:space="preserve">    49: "cellMax",</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    26: "psiFLValue",</t>
+          <t xml:space="preserve">    50: "cellBar",</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">    27: "psiFRValue",</t>
+          <t xml:space="preserve">    # page_4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">    28: "psiRLValue",</t>
+          <t xml:space="preserve">    51: "running_perc",</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    29: "psiRRValue",</t>
+          <t xml:space="preserve">    52: "gated_percent",</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">    30: "socValue",</t>
+          <t xml:space="preserve">    53: "running_temp",</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    31: "socBar",</t>
+          <t xml:space="preserve">    54: "cur_max_temp",</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">    32: "brakeBar",</t>
+          <t xml:space="preserve">    # page_5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    33: "throttleBar",</t>
+          <t xml:space="preserve">    55: "motorFLValue",</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    34: "cardPitMode",</t>
+          <t xml:space="preserve">    56: "motorFRValue",</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
+          <t xml:space="preserve">    57: "motorRLValue",</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    58: "motorRRValue",</t>
+        </is>
+      </c>
+    </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t># uart_data dictionary</t>
+          <t xml:space="preserve">    59: "igbtFLValue",</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>uart_data = {</t>
+          <t xml:space="preserve">    60: "igbtFRValue",</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "frontbrakebar": 0,</t>
+          <t xml:space="preserve">    61: "igbtRLValue",</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "rearbrakebar": 0,</t>
+          <t xml:space="preserve">    62: "igbtRRValue",</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "speedbar": 0,</t>
+          <t xml:space="preserve">    63: "coldPlateFLValue",</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "throttlebar": 0,</t>
+          <t xml:space="preserve">    64: "coldPlateFRValue",</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "front_brake_text": 0,</t>
+          <t xml:space="preserve">    65: "coldPlateRLValue",</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "rear_brake_text": 0,</t>
+          <t xml:space="preserve">    66: "coldPlateRRValue",</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "speed_text": 0,</t>
+          <t xml:space="preserve">    67: "motorLoopStartValue",</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "throttle_text": 0,</t>
+          <t xml:space="preserve">    68: "motorLoopEndValue",</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    # page_2</t>
+          <t xml:space="preserve">    69: "inverterLoopStartValue",</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "valCurrent": 0,</t>
+          <t xml:space="preserve">    70: "inverterLoopEndValue",</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "valVoltage": 0,</t>
+          <t xml:space="preserve">    # page_6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "valMinTemp": 0,</t>
+          <t xml:space="preserve">    71: "can1_util_bar_1",</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "valMaxTemp": 0,</t>
+          <t xml:space="preserve">    72: "can1_util_bar_2",</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "valMinVolt": 0,</t>
+          <t xml:space="preserve">    73: "can1_util_bar_3",</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "valMaxVolt": 0,</t>
+          <t xml:space="preserve">    74: "can1_util_bar_4",</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "badgeCharging": 0,</t>
+          <t xml:space="preserve">    75: "barPercentStyle",</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "badgeBalancing": 0,</t>
+          <t xml:space="preserve">    76: "barPercentStyle2",</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "dotCharging": 0,</t>
+          <t xml:space="preserve">    77: "barPercentStyle3",</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "dotBalancing": 0,</t>
+          <t xml:space="preserve">    78: "barPercentStyle4",</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">    # page_10</t>
+          <t xml:space="preserve">    79: "tableRowValue",</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "tireFLValue": 0,</t>
+          <t xml:space="preserve">    80: "tableRowValue2",</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "tireFRValue": 0,</t>
+          <t xml:space="preserve">    81: "tableRowValue3",</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "tireRLValue": 0,</t>
+          <t xml:space="preserve">    82: "tableRowValue4",</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "tireRRValue": 0,</t>
+          <t xml:space="preserve">    83: "l1_light",</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "maxCellValue": 0,</t>
+          <t xml:space="preserve">    84: "l2_light",</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "maxCellBar": 0,</t>
+          <t xml:space="preserve">    85: "l3_light",</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "speedValue": 0,</t>
+          <t xml:space="preserve">    86: "l4_light",</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "psiFLValue": 0,</t>
+          <t xml:space="preserve">    # page_10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "psiFRValue": 0,</t>
+          <t xml:space="preserve">    19: "tireFLValue",</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "psiRLValue": 0,</t>
+          <t xml:space="preserve">    20: "tireFRValue",</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "psiRRValue": 0,</t>
+          <t xml:space="preserve">    21: "tireRLValue",</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "socValue": 0,</t>
+          <t xml:space="preserve">    22: "tireRRValue",</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "socBar": 0,</t>
+          <t xml:space="preserve">    23: "maxCellValue",</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "brakeBar": 0,</t>
+          <t xml:space="preserve">    24: "maxCellBar",</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "throttleBar": 0,</t>
+          <t xml:space="preserve">    25: "speedValue",</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "cardPitMode": 0,</t>
+          <t xml:space="preserve">    26: "psiFLValue",</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>}</t>
-        </is>
-      </c>
-    </row>
-    <row r="80"/>
+          <t xml:space="preserve">    27: "psiFRValue",</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    28: "psiRLValue",</t>
+        </is>
+      </c>
+    </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t># pages dictionary</t>
+          <t xml:space="preserve">    29: "psiRRValue",</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>pages = {</t>
+          <t xml:space="preserve">    30: "socValue",</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "page_1": {</t>
+          <t xml:space="preserve">    31: "socBar",</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "frontbrakebar": "bar",</t>
+          <t xml:space="preserve">    32: "brakeBar",</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "rearbrakebar": "bar",</t>
+          <t xml:space="preserve">    33: "throttleBar",</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "speedbar": "bar",</t>
+          <t xml:space="preserve">    34: "cardPitMode",</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "throttlebar": "bar",</t>
+          <t xml:space="preserve">    35: "torqueFL",</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "front_brake_text": "text",</t>
+          <t xml:space="preserve">    36: "torqueFR",</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "rear_brake_text": "text",</t>
+          <t xml:space="preserve">    37: "torqueRL",</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "speed_text": "text",</t>
+          <t xml:space="preserve">    38: "torqueRR",</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "throttle_text": "text",</t>
+          <t xml:space="preserve">    39: "torqueBarFL",</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">    40: "torqueBarFR",</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "page_2": {</t>
+          <t xml:space="preserve">    41: "torqueBarRL",</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "valCurrent": "text",</t>
+          <t xml:space="preserve">    42: "torqueBarRR",</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "valVoltage": "text",</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        "valMinTemp": "text",</t>
-        </is>
-      </c>
-    </row>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96"/>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "valMaxTemp": "text",</t>
+          <t># uart_data dictionary</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "valMinVolt": "text",</t>
+          <t>uart_data = {</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "valMaxVolt": "text",</t>
+          <t xml:space="preserve">    "frontbrakebar": 0,</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "badgeCharging": "badge",</t>
+          <t xml:space="preserve">    "rearbrakebar": 0,</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "badgeBalancing": "badge",</t>
+          <t xml:space="preserve">    "speedbar": 0,</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "dotCharging": "led",</t>
+          <t xml:space="preserve">    "throttlebar": 0,</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "dotBalancing": "led",</t>
+          <t xml:space="preserve">    "front_brake_text": 0,</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">    "rear_brake_text": 0,</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "page_10": {</t>
+          <t xml:space="preserve">    "speed_text": 0,</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "tireFLValue": "text",</t>
+          <t xml:space="preserve">    "throttle_text": 0,</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "tireFRValue": "text",</t>
+          <t xml:space="preserve">    # page_2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "tireRLValue": "text",</t>
+          <t xml:space="preserve">    "valCurrent": 0,</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "tireRRValue": "text",</t>
+          <t xml:space="preserve">    "valVoltage": 0,</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "maxCellValue": "text",</t>
+          <t xml:space="preserve">    "valMinTemp": 0,</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "maxCellBar": "bar",</t>
+          <t xml:space="preserve">    "valMaxTemp": 0,</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "speedValue": "text",</t>
+          <t xml:space="preserve">    "valMinVolt": 0,</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "psiFLValue": "text",</t>
+          <t xml:space="preserve">    "valMaxVolt": 0,</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "psiFRValue": "text",</t>
+          <t xml:space="preserve">    "badgeCharging": 0,</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "psiRLValue": "text",</t>
+          <t xml:space="preserve">    "badgeBalancing": 0,</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "psiRRValue": "text",</t>
+          <t xml:space="preserve">    "dotCharging": 0,</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "socValue": "text",</t>
+          <t xml:space="preserve">    "dotBalancing": 0,</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "socBar": "bar",</t>
+          <t xml:space="preserve">    # page_10</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "brakeBar": "bar",</t>
+          <t xml:space="preserve">    "tireFLValue": 0,</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "throttleBar": "bar",</t>
+          <t xml:space="preserve">    "tireFRValue": 0,</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">        "cardPitMode": "badge",</t>
+          <t xml:space="preserve">    "tireRLValue": 0,</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">    },</t>
+          <t xml:space="preserve">    "tireRRValue": 0,</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "maxCellValue": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "maxCellBar": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "speedValue": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "psiFLValue": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "psiFRValue": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "psiRLValue": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "psiRRValue": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "socValue": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "socBar": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "brakeBar": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "throttleBar": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "cardPitMode": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "torqueFL": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "torqueFR": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "torqueRL": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "torqueRR": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "torqueBarFL": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "torqueBarFR": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "torqueBarRL": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "torqueBarRR": 0,</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>}</t>
+        </is>
+      </c>
+    </row>
+    <row r="144"/>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t># pages dictionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>pages = {</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "page_1": {</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "frontbrakebar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "rearbrakebar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "speedbar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "throttlebar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "front_brake_text": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "rear_brake_text": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "speed_text": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "throttle_text": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    },</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "page_2": {</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "valCurrent": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "valVoltage": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "valMinTemp": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "valMaxTemp": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "valMinVolt": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "valMaxVolt": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "badgeCharging": "badge",</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "badgeBalancing": "badge",</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "dotCharging": "led",</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "dotBalancing": "led",</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    },</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "page_10": {</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "tireFLValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "tireFRValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "tireRLValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "tireRRValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "maxCellValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "maxCellBar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "speedValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "psiFLValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "psiFRValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "psiRLValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "psiRRValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "socValue": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "socBar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "brakeBar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "throttleBar": "bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "cardPitMode": "badge",</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "torqueFL": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "torqueFR": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "torqueRL": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "torqueRR": "text",</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "torqueBarFL": "progress_bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "torqueBarFR": "progress_bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "torqueBarRL": "progress_bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        "torqueBarRR": "progress_bar",</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    },</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>}</t>
         </is>
